--- a/ClientExcel/GameHotfix/Guide.xlsx
+++ b/ClientExcel/GameHotfix/Guide.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>#</t>
   </si>
@@ -38,10 +38,10 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>NextId</t>
+    <t>StepName</t>
+  </si>
+  <si>
+    <t>NextStepId</t>
   </si>
   <si>
     <t>Int32</t>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>策划备注</t>
+  </si>
+  <si>
+    <t>步骤编号枚举名</t>
   </si>
   <si>
     <t>步骤名称</t>
@@ -1013,14 +1016,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="8" width="23.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="1" customWidth="1"/>
-    <col min="10" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="21.875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="1" max="6" width="23.625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1031,35 +1031,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1075,16 +1075,14 @@
       <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:6">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
